--- a/v1.2/A2PICO2.v1.2_BOM.xlsx
+++ b/v1.2/A2PICO2.v1.2_BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ralle\Documents\A2PICO2.v1.2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A36EEEA-6574-4AF4-A9D4-162535B7C8CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C684CCE4-D2D3-49B4-9609-7FBF562FC917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -206,9 +206,6 @@
     <t>RP2354B-A2</t>
   </si>
   <si>
-    <t>C6848499</t>
-  </si>
-  <si>
     <t>C19702</t>
   </si>
   <si>
@@ -285,6 +282,9 @@
   </si>
   <si>
     <t>C51939610</t>
+  </si>
+  <si>
+    <t>C397049</t>
   </si>
 </sst>
 </file>
@@ -794,52 +794,52 @@
     </row>
     <row r="2" spans="1:5" ht="20" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="20" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="20" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="20" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>4</v>
@@ -899,7 +899,7 @@
         <v>34</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="1" customFormat="1" ht="20" customHeight="1">
@@ -925,7 +925,7 @@
         <v>22</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="E11" s="12"/>
     </row>
@@ -934,7 +934,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>4</v>
@@ -962,7 +962,7 @@
         <v>36</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>4</v>
@@ -973,16 +973,16 @@
     </row>
     <row r="15" spans="1:5" ht="20" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="20" customHeight="1">
@@ -990,13 +990,13 @@
         <v>47</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="20" customHeight="1">
@@ -1004,7 +1004,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>4</v>
@@ -1018,7 +1018,7 @@
         <v>27</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>29</v>
@@ -1053,16 +1053,16 @@
     </row>
     <row r="21" spans="1:4" ht="20" customHeight="1">
       <c r="A21" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="20" customHeight="1">
@@ -1070,7 +1070,7 @@
         <v>37</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>38</v>
@@ -1087,7 +1087,7 @@
         <v>21</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/v1.2/A2PICO2.v1.2_BOM.xlsx
+++ b/v1.2/A2PICO2.v1.2_BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ralle\Documents\A2PICO2.v1.2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C684CCE4-D2D3-49B4-9609-7FBF562FC917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F049C7AD-82D9-44C6-A8E2-06F28CDF6C21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -185,12 +185,6 @@
     <t>C25190</t>
   </si>
   <si>
-    <t>ABM8-272-T3</t>
-  </si>
-  <si>
-    <t>C42411119</t>
-  </si>
-  <si>
     <t>R1,R2</t>
   </si>
   <si>
@@ -285,6 +279,12 @@
   </si>
   <si>
     <t>C397049</t>
+  </si>
+  <si>
+    <t>C48783272</t>
+  </si>
+  <si>
+    <t>12MHz</t>
   </si>
 </sst>
 </file>
@@ -794,52 +794,52 @@
     </row>
     <row r="2" spans="1:5" ht="20" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="20" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="20" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="20" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>4</v>
@@ -899,7 +899,7 @@
         <v>34</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="1" customFormat="1" ht="20" customHeight="1">
@@ -911,7 +911,7 @@
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="4" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="20" customHeight="1">
@@ -919,13 +919,13 @@
         <v>12</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>22</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E11" s="12"/>
     </row>
@@ -934,7 +934,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>4</v>
@@ -948,7 +948,7 @@
         <v>27</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>4</v>
@@ -962,7 +962,7 @@
         <v>36</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>4</v>
@@ -973,16 +973,16 @@
     </row>
     <row r="15" spans="1:5" ht="20" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="20" customHeight="1">
@@ -990,13 +990,13 @@
         <v>47</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="20" customHeight="1">
@@ -1004,7 +1004,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>4</v>
@@ -1018,7 +1018,7 @@
         <v>27</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>29</v>
@@ -1032,7 +1032,7 @@
         <v>15</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C19" s="4"/>
       <c r="D19" s="4" t="s">
@@ -1041,28 +1041,28 @@
     </row>
     <row r="20" spans="1:4" ht="20" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="4"/>
       <c r="D20" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="20" customHeight="1">
       <c r="A21" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="20" customHeight="1">
@@ -1070,7 +1070,7 @@
         <v>37</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>38</v>
@@ -1078,7 +1078,7 @@
     </row>
     <row r="23" spans="1:4" ht="20" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>35</v>
@@ -1087,7 +1087,7 @@
         <v>21</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
